--- a/AAII_Financials/Quarterly/NRIX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NRIX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="92">
   <si>
     <t>NRIX</t>
   </si>
@@ -656,289 +656,296 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E7" s="2">
         <v>46081</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45991</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45900</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45808</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45716</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45626</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45535</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45443</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45351</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45260</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45169</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45077</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44985</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44895</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44804</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44712</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44620</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44530</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44439</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44347</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44255</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44165</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44074</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43982</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43890</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43799</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43708</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43616</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43524</v>
       </c>
-      <c r="AG7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E8" s="3">
         <v>6300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>13600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>44100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>18500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>12600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>12100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>16600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>15200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>18500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>30700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>12700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>11400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>9600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>7400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>10300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>10600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>9400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>9200</v>
       </c>
-      <c r="AG8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>87700</v>
+      </c>
+      <c r="E9" s="3">
         <v>84100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>83000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>86100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>78100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>69700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>67200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>55500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>48900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>50000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>49700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>47900</v>
-      </c>
-      <c r="O9" s="3">
-        <v>45800</v>
       </c>
       <c r="P9" s="3">
         <v>45800</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
+      <c r="Q9" s="3">
+        <v>45800</v>
       </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
@@ -991,53 +998,56 @@
       <c r="AH9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-78600</v>
+      </c>
+      <c r="E10" s="3">
         <v>-77900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-69400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-78200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-34000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-51200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-53900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-42900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-36800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-33400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-34600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-29400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-15100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-33100</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1089,8 +1099,11 @@
       <c r="AH10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,106 +1138,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>87700</v>
+      </c>
+      <c r="E12" s="3">
         <v>84100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>83000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>86100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>78100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>69700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>67200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>55500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>48900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>50000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>49700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>47900</v>
-      </c>
-      <c r="O12" s="3">
-        <v>45800</v>
       </c>
       <c r="P12" s="3">
         <v>45800</v>
       </c>
       <c r="Q12" s="3">
+        <v>45800</v>
+      </c>
+      <c r="R12" s="3">
         <v>46100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>47800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>47500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>43100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>36500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>30900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>26000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>23000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>20400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>18900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>14100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>13000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>12800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>11000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>10800</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>10400</v>
       </c>
-      <c r="AG12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,8 +1338,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1365,8 +1385,8 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1419,53 +1439,56 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E15" s="3">
         <v>2200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1800</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>103200</v>
+      </c>
+      <c r="E17" s="3">
         <v>98700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>96700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>99300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>92400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>81300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>77900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>67200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>60600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>61800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>60500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>58500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>57400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>55600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>55500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>57500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>57100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>52400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>45300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>39200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>33500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>29500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>26700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>23300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>17400</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>15400</v>
       </c>
       <c r="AC17" s="3">
         <v>15400</v>
       </c>
       <c r="AD17" s="3">
+        <v>15400</v>
+      </c>
+      <c r="AE17" s="3">
         <v>13200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>12600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>12100</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-94200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-92500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-83100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-91400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-48300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-62900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-64700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-54600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-48500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-45200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-45300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-40000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-26800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-43000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-48700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-46700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-45700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-42800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-37900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-28900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-26400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-24500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-20000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-19200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-13200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-12500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-13500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-3200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,8 +1815,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1826,44 +1860,44 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3">
         <v>2000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>300</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>100</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>200</v>
       </c>
       <c r="AD20" s="3">
         <v>200</v>
@@ -1874,112 +1908,118 @@
       <c r="AF20" s="3">
         <v>200</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>3</v>
+      <c r="AG20" s="3">
+        <v>200</v>
       </c>
       <c r="AH20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-91900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-90300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-81600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-89400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-46100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-60500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-63400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-52200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-46200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-43200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-44800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-38100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-24900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-41200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-45100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-44300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-44100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-41500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-36900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-28200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-25600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-23600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-19200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-18000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-12500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-11900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-12800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-2500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2022,8 +2062,8 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2076,129 +2116,135 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-89800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-87200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-78200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-86400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-42700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-56400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-58500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-48900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-44500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-41400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-42000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-37000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-24300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-40700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-46700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-45700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-45400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-42500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-37700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-29000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-26200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-24200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-19900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-18500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-13000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-12400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-13300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-2700</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="D24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3">
         <v>800</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3">
         <v>100</v>
@@ -2206,8 +2252,8 @@
       <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
+      <c r="M24" s="3">
+        <v>100</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
@@ -2218,8 +2264,8 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -2234,46 +2280,49 @@
         <v>0</v>
       </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>-100</v>
-      </c>
-      <c r="W24" s="3">
-        <v>100</v>
       </c>
       <c r="X24" s="3">
         <v>100</v>
       </c>
       <c r="Y24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z24" s="3">
         <v>0</v>
       </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
         <v>-20600</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
       <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3">
         <v>200</v>
       </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
       <c r="AE24" s="3">
         <v>0</v>
       </c>
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-      <c r="AG24" s="3" t="s">
-        <v>3</v>
+      <c r="AG24" s="3">
+        <v>0</v>
       </c>
       <c r="AH24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-89500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-87200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-78200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-86400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-43500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-56400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-58500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-49000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-44500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-41500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-42000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-37000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-24300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-40700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-46700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-45700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-45400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-42500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-37700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-28800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-26400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-24300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-19900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-18500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>7600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-12400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-13500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-2700</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-89500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-87200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-78200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-86400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-43500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-56400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-58500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-49000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-44500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-41500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-42000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-37000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-24300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-40700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-46700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-45700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-45400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-42500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-37700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-28800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-26400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-24300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-19900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-18500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>7600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-12400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-13500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-2700</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,8 +3025,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3002,44 +3072,44 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3">
         <v>-2000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-300</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-100</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>-200</v>
       </c>
       <c r="AD32" s="3">
         <v>-200</v>
@@ -3050,112 +3120,118 @@
       <c r="AF32" s="3">
         <v>-200</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>3</v>
+      <c r="AG32" s="3">
+        <v>-200</v>
       </c>
       <c r="AH32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-89500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-87200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-78200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-86400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-43500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-56400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-58500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-49000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-44500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-41500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-42000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-37000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-24300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-40700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-46700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-45700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-45400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-42500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-37700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-28800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-26400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-24300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-19900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-18500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>7600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-12400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-13500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-2700</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-89500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-87200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-78200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-86400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-43500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-56400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-58500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-49000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-44500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-41500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-42000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-37000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-24300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-40700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-46700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-45700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-45400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-42500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-37700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-28800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-26400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-24300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-19900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-18500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>7600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-12400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-13500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-2700</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E38" s="2">
         <v>46081</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45991</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45900</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45808</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45716</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45626</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45535</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45443</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45351</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45260</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45169</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45077</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44985</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44895</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44804</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44712</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44620</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44530</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44439</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44347</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44255</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44165</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44074</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43982</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43890</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43799</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43708</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43616</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43524</v>
       </c>
-      <c r="AG38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,89 +3611,90 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>67700</v>
+      </c>
+      <c r="E41" s="3">
         <v>71200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>247000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>78400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>84300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>75900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>110000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>99000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>116800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>49800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>54600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>42300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>59000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>33600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>64500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>47600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>41500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>78800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>80200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>147400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>188200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>126400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>119200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>265400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>159200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>56200</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3623,89 +3710,92 @@
       <c r="AH41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>375800</v>
+      </c>
+      <c r="E42" s="3">
         <v>469500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>346000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>350400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>401500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>473800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>499600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>349000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>326300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>194200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>233300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>216500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>222200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>243600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>244700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>296900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>255700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>183200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>215200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>196500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>197800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>176700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>161800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>88700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>14200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>14900</v>
       </c>
-      <c r="AC42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3721,53 +3811,56 @@
       <c r="AH42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E43" s="3">
         <v>2400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>20700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>600</v>
-      </c>
-      <c r="L43" s="3">
-        <v>800</v>
       </c>
       <c r="M43" s="3">
         <v>800</v>
       </c>
       <c r="N43" s="3">
+        <v>800</v>
+      </c>
+      <c r="O43" s="3">
         <v>2800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1200</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -3775,32 +3868,32 @@
         <v>0</v>
       </c>
       <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3">
         <v>8200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>11300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>19600</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3819,8 +3912,11 @@
       <c r="AH43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3863,8 +3959,8 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3917,8 +4013,11 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3961,45 +4060,45 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3">
         <v>9300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>10400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>9500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>10300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>9500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>9300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>4600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>6100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>6200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>5500</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4015,89 +4114,92 @@
       <c r="AH45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>456500</v>
+      </c>
+      <c r="E46" s="3">
         <v>554400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>606800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>440600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>515300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>563700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>619400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>456000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>450200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>251000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>295500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>267900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>290000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>288300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>318400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>354900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>306800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>280500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>311100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>358400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>396300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>310800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>298400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>364100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>196800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>76700</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4113,8 +4215,11 @@
       <c r="AH46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4136,66 +4241,66 @@
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3">
         <v>9500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>10300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>7400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>9900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>27500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>48400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>63900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>69100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>51500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>123700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>137200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>121500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>110400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>77200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>90900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>40900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>9100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>7600</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4211,89 +4316,92 @@
       <c r="AH47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>70100</v>
+      </c>
+      <c r="E48" s="3">
         <v>73400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>73000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>73500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>69000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>44800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>45900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>44200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>47400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>47200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>48000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>25600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>28400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>28600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>29500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>30300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>30900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>29400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>25300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>9600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>8300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4000</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4309,8 +4417,11 @@
       <c r="AH48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,89 +4720,92 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E52" s="3">
         <v>8400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4000</v>
-      </c>
-      <c r="L52" s="3">
-        <v>4200</v>
       </c>
       <c r="M52" s="3">
         <v>4200</v>
       </c>
       <c r="N52" s="3">
+        <v>4200</v>
+      </c>
+      <c r="O52" s="3">
         <v>4800</v>
-      </c>
-      <c r="O52" s="3">
-        <v>4700</v>
       </c>
       <c r="P52" s="3">
         <v>4700</v>
       </c>
       <c r="Q52" s="3">
+        <v>4700</v>
+      </c>
+      <c r="R52" s="3">
         <v>4900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>600</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4701,8 +4821,11 @@
       <c r="AH52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,89 +4922,92 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>535500</v>
+      </c>
+      <c r="E54" s="3">
         <v>636100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>688100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>522500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>591600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>615000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>669300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>513600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>511000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>312700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>355600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>308200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>350600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>370200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>416800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>459300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>394300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>437700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>476800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>493100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>518000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>396700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>396300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>411900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>213300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>88800</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4897,8 +5023,11 @@
       <c r="AH54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,89 +5099,90 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E57" s="3">
         <v>10300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>11500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5100</v>
-      </c>
-      <c r="R57" s="3">
-        <v>6100</v>
       </c>
       <c r="S57" s="3">
         <v>6100</v>
       </c>
       <c r="T57" s="3">
+        <v>6100</v>
+      </c>
+      <c r="U57" s="3">
         <v>6000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>4900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2100</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5067,8 +5198,11 @@
       <c r="AH57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5076,43 +5210,43 @@
         <v>3200</v>
       </c>
       <c r="E58" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F58" s="3">
         <v>2800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>8000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5400</v>
-      </c>
-      <c r="O58" s="3">
-        <v>5600</v>
       </c>
       <c r="P58" s="3">
         <v>5600</v>
       </c>
       <c r="Q58" s="3">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -5165,89 +5299,92 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E59" s="3">
         <v>21700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>20700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>28700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>29400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>34600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>41900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>49600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>48500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>47200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>48900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>32900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>45300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>39400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>65600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>61400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>66500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>60000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>59600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>46800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>41400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>43600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>41100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>37400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>29500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>27900</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5263,89 +5400,92 @@
       <c r="AH59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>72000</v>
+      </c>
+      <c r="E60" s="3">
         <v>92200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>86500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>82400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>75600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>90000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>95900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>86300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>80800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>87600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>87000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>61500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>72300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>64900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>70700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>67500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>72700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>66000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>66300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>50700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>46800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>48000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>44500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>41000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>34400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>30000</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5361,53 +5501,56 @@
       <c r="AH60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>54900</v>
+      </c>
+      <c r="E61" s="3">
         <v>55500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>52900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>52700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>46700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>20000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>20300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>20600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>20900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>21800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>23100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5100</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -5459,8 +5602,11 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5503,45 +5649,45 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3">
         <v>42400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>49300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>54900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>65800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>68200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>67200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>73000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>78600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>61500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>63200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>72300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>80400</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,89 +6006,92 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>132900</v>
+      </c>
+      <c r="E66" s="3">
         <v>155200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>149400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>150200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>144000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>134100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>142400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>136700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>140300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>143900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>155100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>74400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>90700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>96100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>113100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>116800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>127600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>131800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>134500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>117900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>119800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>126500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>106100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>104300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>106700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>110400</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5949,8 +6107,11 @@
       <c r="AH66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6256,14 +6424,14 @@
         <v>0</v>
       </c>
       <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
         <v>168100</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>48200</v>
       </c>
-      <c r="AC70" s="3">
-        <v>0</v>
-      </c>
       <c r="AD70" s="3">
         <v>0</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,89 +6548,92 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1179900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1090400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1003200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-925000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-838600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-795100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-738800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-680200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-631300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-586700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-545200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-503200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-466300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-442000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-401300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-354500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-308800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-263400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-220900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-183200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-154400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-128000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-103700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-83800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-65300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-72800</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6475,8 +6649,11 @@
       <c r="AH72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,89 +6952,92 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>402600</v>
+      </c>
+      <c r="E76" s="3">
         <v>480900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>538700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>372300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>447600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>480900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>527000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>376900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>370700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>168700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>200500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>233800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>259900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>274100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>303700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>342500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>266700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>305900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>342300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>375200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>398200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>270100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>290300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>307600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-61500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-69800</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6867,8 +7053,11 @@
       <c r="AH76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E80" s="2">
         <v>46081</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45991</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45900</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45808</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45716</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45626</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45535</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45443</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45351</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45260</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45169</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45077</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44985</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44895</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44804</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44712</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44620</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44530</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44439</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44347</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44255</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44165</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44074</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43982</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43890</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43799</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43708</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43616</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43524</v>
       </c>
-      <c r="AG80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-89500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-87200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-78200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-86400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-43500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-56400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-58500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-49000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-44500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-41500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-42000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-37000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-24300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-40700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-46700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-45700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-45400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-42500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-37700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-28800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-26400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-24300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-19900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-18500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>7600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-12400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-13500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-2700</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,70 +7400,71 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E83" s="3">
         <v>4100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3000</v>
-      </c>
-      <c r="F83" s="3">
-        <v>4100</v>
       </c>
       <c r="G83" s="3">
         <v>4100</v>
       </c>
       <c r="H83" s="3">
+        <v>4100</v>
+      </c>
+      <c r="I83" s="3">
         <v>3900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>700</v>
-      </c>
-      <c r="W83" s="3">
-        <v>600</v>
       </c>
       <c r="X83" s="3">
         <v>600</v>
@@ -7277,7 +7476,7 @@
         <v>600</v>
       </c>
       <c r="AA83" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AB83" s="3">
         <v>500</v>
@@ -7286,7 +7485,7 @@
         <v>500</v>
       </c>
       <c r="AD83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AE83" s="3">
         <v>600</v>
@@ -7294,14 +7493,17 @@
       <c r="AF83" s="3">
         <v>600</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>3</v>
+      <c r="AG83" s="3">
+        <v>600</v>
       </c>
       <c r="AH83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-96600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-71900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-67800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-57400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-63200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-61100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-48800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-42200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-39700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-42000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>26700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-41100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-18500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-48500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-38000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-46300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-32900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-42600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-30900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-30000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-31500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>8100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-20500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-14400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>41000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-12700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>36400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-13300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-9700</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,106 +8144,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5100</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-2700</v>
       </c>
       <c r="G91" s="3">
         <v>-2700</v>
       </c>
       <c r="H91" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="I91" s="3">
         <v>-3500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-500</v>
       </c>
-      <c r="AE91" s="3">
-        <v>0</v>
-      </c>
       <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-200</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>93000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-123800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>50500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>71500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>25500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-140800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-21300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-131100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>35500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-14400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>22800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>43800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>16100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>55000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-63100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>40000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-36500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-12200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-57100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-124600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-108100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-19400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-4400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>3500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>10000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-600</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8396,8 +8630,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,106 +8987,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>20000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>236000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1200</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>1500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>200500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>45800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>237800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1600</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>1700</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>1500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>115400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>150500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>220400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>119700</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>100</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
         <v>0</v>
       </c>
       <c r="AF100" s="3">
         <v>0</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>3</v>
+      <c r="AG100" s="3">
+        <v>0</v>
       </c>
       <c r="AH100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8886,8 +9135,8 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -8940,102 +9189,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-175800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>168500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>8300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-34100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>11000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-17700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>67000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>12300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-16700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>25400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-30900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>16900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>6000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-37200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-66900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-40700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>61800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>7000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-146200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>106200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>102900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>21600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-17000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>39900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-3300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-10300</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
